--- a/academias/Ciencias Sociales - Estadisticos 20232.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20232.xlsx
@@ -744,25 +744,25 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>96.8</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>3.2</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J2">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -779,25 +779,25 @@
         <v>31</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="J3">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -814,25 +814,25 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>16</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J4">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -849,25 +849,25 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>88</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -881,25 +881,25 @@
         <v>112</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F6">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J6">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -910,25 +910,25 @@
         <v>112</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="F7">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>7.1</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1008,7 +1008,7 @@
         <v>3.2</v>
       </c>
       <c r="I2" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1066,19 +1066,19 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G4" s="1">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="H4" s="1">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I4" s="2">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1101,19 +1101,19 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G5" s="1">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="H5" s="1">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I5" s="2">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1133,19 +1133,19 @@
         <v>112</v>
       </c>
       <c r="E6">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>97.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>2.7</v>
+        <v>7.1</v>
       </c>
       <c r="I6" s="2">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1162,19 +1162,19 @@
         <v>112</v>
       </c>
       <c r="E7">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>97.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>2.7</v>
+        <v>7.1</v>
       </c>
       <c r="I7" s="2">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="J7">
         <v>0</v>

--- a/academias/Ciencias Sociales - Estadisticos 20232.xlsx
+++ b/academias/Ciencias Sociales - Estadisticos 20232.xlsx
@@ -489,22 +489,22 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>96.8</v>
+        <v>97</v>
       </c>
       <c r="H2" s="1">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I2" s="2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -524,10 +524,10 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -539,7 +539,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -626,19 +626,19 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E6">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F6">
         <v>3</v>
       </c>
       <c r="G6" s="1">
-        <v>97.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H6" s="1">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="I6" s="2">
         <v>8.300000000000001</v>
@@ -655,19 +655,19 @@
         <v>15</v>
       </c>
       <c r="D7">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E7">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F7">
         <v>3</v>
       </c>
       <c r="G7" s="1">
-        <v>97.3</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="H7" s="1">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="I7" s="2">
         <v>8.300000000000001</v>
@@ -741,19 +741,19 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F2">
         <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>96.8</v>
+        <v>97</v>
       </c>
       <c r="H2" s="1">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="I2" s="2">
         <v>8.300000000000001</v>
@@ -776,10 +776,10 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -878,19 +878,19 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E6">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F6">
         <v>8</v>
       </c>
       <c r="G6" s="1">
-        <v>92.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H6" s="1">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="I6" s="2">
         <v>7.6</v>
@@ -907,19 +907,19 @@
         <v>15</v>
       </c>
       <c r="D7">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E7">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F7">
         <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>92.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H7" s="1">
-        <v>7.1</v>
+        <v>6.9</v>
       </c>
       <c r="I7" s="2">
         <v>7.6</v>
@@ -993,19 +993,19 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
         <v>8.5</v>
@@ -1028,10 +1028,10 @@
         <v>16</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1043,7 +1043,7 @@
         <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1066,16 +1066,16 @@
         <v>25</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
         <v>7.4</v>
@@ -1101,19 +1101,19 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1130,22 +1130,22 @@
         <v>14</v>
       </c>
       <c r="D6">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E6">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6" s="1">
+        <v>100</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
         <v>8</v>
-      </c>
-      <c r="G6" s="1">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="H6" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="I6" s="2">
-        <v>8.199999999999999</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1159,22 +1159,22 @@
         <v>15</v>
       </c>
       <c r="D7">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E7">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7" s="1">
+        <v>100</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
         <v>8</v>
-      </c>
-      <c r="G7" s="1">
-        <v>92.90000000000001</v>
-      </c>
-      <c r="H7" s="1">
-        <v>7.1</v>
-      </c>
-      <c r="I7" s="2">
-        <v>8.1</v>
       </c>
       <c r="J7">
         <v>0</v>
